--- a/data/trans_camb/IQ2601_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IQ2601_R2-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>13.8561833270113</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>30.88549984633362</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>15.14954117102986</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>19.87101451806392</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>14.44057655883914</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>26.40587577166337</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>7.352665909228313</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>16.13155238873609</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8.275264877596827</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.1232537328394629</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>9.039720075635328</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>14.8161441263765</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>20.72592973114949</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>42.70563953380089</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>22.37398872510259</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>34.79686337375711</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>19.56921502547883</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>36.53159741905277</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.2875487302725126</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.6409475145534697</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.2974248471876511</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.3901196339728479</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2916200568119002</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5332531538006323</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>0.1421348349939467</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.343435103733879</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.151692529411723</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.001826675866093753</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.170932855575882</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.2949161467303859</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.4759479952670628</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.9704646812916649</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.4789800968553582</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.7365167972455871</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4201514023341891</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.7696399068249448</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>21.56802630980363</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>21.9585812854633</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>17.68244188027847</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>35.01860919404915</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>19.62607763204981</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>27.12257708022963</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>13.44596712511477</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.011373020882705</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>10.18351160058464</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>22.76727481420732</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>14.020096047904</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>17.2216620864165</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>29.19560418067282</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>36.11612914820714</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>25.51169801035095</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>45.6456124872798</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>25.24632997221305</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>36.22522105308035</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.4524578017799988</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.460650931889493</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.3571910428789343</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.7073872275606352</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4039382574012433</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.5582290423700211</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>0.2591025884078395</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.11197575415906</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.1894616862793728</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.4456521373928258</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.2672493562747841</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.3381872678598323</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.6722783666100151</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.7920950279536543</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.5680520913536359</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.9964537843258318</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5585718654628643</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7661789927536162</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>16.351633003375</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>25.65831902283769</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.793083301210489</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>12.6454562750965</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>11.10351922617389</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>19.52367421182674</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>7.327114102755197</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>12.9599786422073</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.604843058017091</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.5641787183443803</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4.198203751701814</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>9.227518097391584</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>25.73239962208177</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>35.20905172433962</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>15.14941642677655</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>25.45770430077113</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>17.68520299565374</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>26.96890916838178</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.3385999525244989</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.5313173064242629</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.1025979740082951</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.2239564195398825</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.212178825797061</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.3730808390681021</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>0.1405258400834788</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.2382705781630848</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.05873647529511496</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.00689538609120377</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.07409859035294433</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.1683840185212971</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.5998303421600529</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.8096283521741774</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.2963040715743812</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.5052788289935567</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.360747097891908</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.5543683491597383</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>5.697889266795775</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>17.81024276863854</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-5.970863574987916</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-3.413642480309198</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.4670946992398561</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>7.790645566156407</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-5.360383908487528</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.535767921740712</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-18.31085276933702</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-20.47055469161615</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-8.155934337590915</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-4.752916822858568</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>18.18023858519065</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>31.66149633008015</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>7.288325967082375</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>11.36632512291959</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>9.156476103416678</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>19.05836243136865</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.1030843284393103</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3222170226868312</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.0985001891918494</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.05631420412154878</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.008091201951858369</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.134952690993293</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.08720895904017535</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.02866991036603177</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.2799263518777086</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.3051285095052294</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.1293465082689437</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.07357792371666771</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.3798525437487393</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.6362369466032693</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.1358385374498466</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.2036095293603552</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.1720570072455123</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.362709413417843</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>15.37600674958385</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>24.65741174277639</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>11.41746750952153</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>16.94517358805112</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>13.44317549720326</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>21.12142172479165</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>10.97794840510197</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>17.85994369124262</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>6.341670783232067</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>9.382694643004193</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>10.53647846209793</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>16.22385159917641</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>19.57611509182579</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>31.51987779550416</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>15.32170380669927</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>23.50092005884331</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>16.28428532054781</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>25.86105587583306</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.3139548175223041</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.5034670789595741</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.2160968655489852</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.3207190119444231</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.2643157708116813</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.4152831944348516</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>0.2160507517728915</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.3590338265996015</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.1175092395045969</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.1822065815415347</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.1988080673176358</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.3118147849074966</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.4231251149099131</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.6775302159830412</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.3044761476265462</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.4535355923081764</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.3286538385302253</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.5177347733868547</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
